--- a/Work/Quick Access/Sheets/UI Elements.xlsx
+++ b/Work/Quick Access/Sheets/UI Elements.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\Ganesh Notes\Docs\Work\Quick Access\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DDACFA4-36DD-4675-B317-E33D072548AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3772158A-D22A-4D59-AB9F-96637F957CAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19500" yWindow="1275" windowWidth="8985" windowHeight="13305" xr2:uid="{58F146A1-B1DA-4048-895A-7747C642247E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58F146A1-B1DA-4048-895A-7747C642247E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -623,7 +624,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -880,7 +881,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B47" s="2"/>
     </row>

--- a/Work/Quick Access/Sheets/UI Elements.xlsx
+++ b/Work/Quick Access/Sheets/UI Elements.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{3772158A-D22A-4D59-AB9F-96637F957CAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58F146A1-B1DA-4048-895A-7747C642247E}"/>
+    <workbookView xWindow="19500" yWindow="1275" windowWidth="8985" windowHeight="13305" xr2:uid="{58F146A1-B1DA-4048-895A-7747C642247E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>

--- a/Work/Quick Access/Sheets/UI Elements.xlsx
+++ b/Work/Quick Access/Sheets/UI Elements.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\Ganesh Notes\Docs\Work\Quick Access\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3772158A-D22A-4D59-AB9F-96637F957CAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6647FDAB-1868-4687-914C-E3D0FAB15398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19500" yWindow="1275" windowWidth="8985" windowHeight="13305" xr2:uid="{58F146A1-B1DA-4048-895A-7747C642247E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{58F146A1-B1DA-4048-895A-7747C642247E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$1</definedName>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="66">
   <si>
     <t>&lt;i class="fa fa-lock fa-4x fa-border"&gt;&lt;/i&gt;</t>
   </si>
@@ -189,13 +190,61 @@
   </si>
   <si>
     <t>&lt;i class="fa fa-fw fa-ban"&gt;&lt;/i&gt;</t>
+  </si>
+  <si>
+    <t>Digital</t>
+  </si>
+  <si>
+    <t>Binary</t>
+  </si>
+  <si>
+    <t>2⁰</t>
+  </si>
+  <si>
+    <t>2¹</t>
+  </si>
+  <si>
+    <t>2²</t>
+  </si>
+  <si>
+    <t>2³</t>
+  </si>
+  <si>
+    <t>2⁴</t>
+  </si>
+  <si>
+    <t>2⁵</t>
+  </si>
+  <si>
+    <t>2⁶</t>
+  </si>
+  <si>
+    <t>2⁷</t>
+  </si>
+  <si>
+    <t>2⁸</t>
+  </si>
+  <si>
+    <t>2⁹</t>
+  </si>
+  <si>
+    <t>2¹⁰</t>
+  </si>
+  <si>
+    <t>Position</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Position of 1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -207,6 +256,20 @@
       <b/>
       <sz val="14"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9" tint="-0.249977111117893"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -247,12 +310,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -899,4 +977,293 @@
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6551A77-643A-46C2-B44E-DE767D422E77}">
+  <dimension ref="D15:K26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="15" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="J15" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D16" s="3">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="K16" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D17" s="3">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6">
+        <v>1</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="K17" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D18" s="3">
+        <v>2</v>
+      </c>
+      <c r="E18" s="5">
+        <v>0</v>
+      </c>
+      <c r="F18" s="5">
+        <v>0</v>
+      </c>
+      <c r="G18" s="6">
+        <v>1</v>
+      </c>
+      <c r="H18" s="5">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="K18" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D19" s="3">
+        <v>3</v>
+      </c>
+      <c r="E19" s="5">
+        <v>0</v>
+      </c>
+      <c r="F19" s="5">
+        <v>0</v>
+      </c>
+      <c r="G19" s="5">
+        <v>1</v>
+      </c>
+      <c r="H19" s="5">
+        <v>1</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K19" s="7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D20" s="3">
+        <v>4</v>
+      </c>
+      <c r="E20" s="5">
+        <v>0</v>
+      </c>
+      <c r="F20" s="6">
+        <v>1</v>
+      </c>
+      <c r="G20" s="5">
+        <v>0</v>
+      </c>
+      <c r="H20" s="5">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="K20" s="7">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D21" s="3">
+        <v>5</v>
+      </c>
+      <c r="E21" s="5">
+        <v>0</v>
+      </c>
+      <c r="F21" s="5">
+        <v>1</v>
+      </c>
+      <c r="G21" s="5">
+        <v>0</v>
+      </c>
+      <c r="H21" s="5">
+        <v>1</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K21" s="7">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D22" s="3">
+        <v>6</v>
+      </c>
+      <c r="E22" s="5">
+        <v>0</v>
+      </c>
+      <c r="F22" s="5">
+        <v>1</v>
+      </c>
+      <c r="G22" s="5">
+        <v>1</v>
+      </c>
+      <c r="H22" s="5">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K22" s="7">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="23" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D23" s="3">
+        <v>7</v>
+      </c>
+      <c r="E23" s="5">
+        <v>0</v>
+      </c>
+      <c r="F23" s="5">
+        <v>1</v>
+      </c>
+      <c r="G23" s="5">
+        <v>1</v>
+      </c>
+      <c r="H23" s="5">
+        <v>1</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K23" s="7">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="24" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D24" s="3">
+        <v>8</v>
+      </c>
+      <c r="E24" s="6">
+        <v>1</v>
+      </c>
+      <c r="F24" s="5">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5">
+        <v>0</v>
+      </c>
+      <c r="H24" s="5">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="K24" s="7">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="25" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D25" s="3">
+        <v>9</v>
+      </c>
+      <c r="E25" s="5">
+        <v>1</v>
+      </c>
+      <c r="F25" s="5">
+        <v>0</v>
+      </c>
+      <c r="G25" s="5">
+        <v>0</v>
+      </c>
+      <c r="H25" s="5">
+        <v>1</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="K25" s="7">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="26" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D26" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E26" s="6">
+        <v>8</v>
+      </c>
+      <c r="F26" s="6">
+        <v>4</v>
+      </c>
+      <c r="G26" s="6">
+        <v>2</v>
+      </c>
+      <c r="H26" s="6">
+        <v>1</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="K26" s="7">
+        <v>1024</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E15:H15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Work/Quick Access/Sheets/UI Elements.xlsx
+++ b/Work/Quick Access/Sheets/UI Elements.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\Ganesh Notes\Docs\Work\Quick Access\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6647FDAB-1868-4687-914C-E3D0FAB15398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A43F1EF-8A21-484F-80F1-7BBB4BE95505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{58F146A1-B1DA-4048-895A-7747C642247E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{58F146A1-B1DA-4048-895A-7747C642247E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
+    <sheet name="Binary" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$1</definedName>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="97">
   <si>
     <t>&lt;i class="fa fa-lock fa-4x fa-border"&gt;&lt;/i&gt;</t>
   </si>
@@ -192,9 +193,6 @@
     <t>&lt;i class="fa fa-fw fa-ban"&gt;&lt;/i&gt;</t>
   </si>
   <si>
-    <t>Digital</t>
-  </si>
-  <si>
     <t>Binary</t>
   </si>
   <si>
@@ -238,13 +236,109 @@
   </si>
   <si>
     <t>Position of 1</t>
+  </si>
+  <si>
+    <t>1 bit system</t>
+  </si>
+  <si>
+    <t>2 bit system</t>
+  </si>
+  <si>
+    <t>4 bit system</t>
+  </si>
+  <si>
+    <t>8 bit system</t>
+  </si>
+  <si>
+    <t>16 bit system</t>
+  </si>
+  <si>
+    <t>Decimal</t>
+  </si>
+  <si>
+    <t>Nibble</t>
+  </si>
+  <si>
+    <t>Byte</t>
+  </si>
+  <si>
+    <t>System Name</t>
+  </si>
+  <si>
+    <t>Alias</t>
+  </si>
+  <si>
+    <t>Range</t>
+  </si>
+  <si>
+    <t>Unique Combos</t>
+  </si>
+  <si>
+    <t>0 to 1</t>
+  </si>
+  <si>
+    <t>0 to 3</t>
+  </si>
+  <si>
+    <t>0 to 15</t>
+  </si>
+  <si>
+    <t>0 to 255</t>
+  </si>
+  <si>
+    <t>0 to 65,535</t>
+  </si>
+  <si>
+    <t>Word</t>
+  </si>
+  <si>
+    <t>Colors</t>
+  </si>
+  <si>
+    <t>Codes</t>
+  </si>
+  <si>
+    <t>Edit Pencil</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Delete Ban</t>
+  </si>
+  <si>
+    <t>#648BDB</t>
+  </si>
+  <si>
+    <t>Thead th</t>
+  </si>
+  <si>
+    <t>#A90329</t>
+  </si>
+  <si>
+    <t>#739E73</t>
+  </si>
+  <si>
+    <t>#C79121</t>
+  </si>
+  <si>
+    <t>Print Button</t>
+  </si>
+  <si>
+    <t>#3276B1</t>
+  </si>
+  <si>
+    <t>New Button</t>
+  </si>
+  <si>
+    <t>Search Button</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -274,16 +368,82 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="9" tint="-0.249977111117893"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FF5B835B"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF648BDB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF739E73"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA90329"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC79121"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3276B1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -306,11 +466,115 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -319,9 +583,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -330,6 +591,76 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -337,6 +668,17 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF3276B1"/>
+      <color rgb="FFC79121"/>
+      <color rgb="FFA90329"/>
+      <color rgb="FF739E73"/>
+      <color rgb="FF648BDB"/>
+      <color rgb="FF77021D"/>
+      <color rgb="FF5B835B"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -980,289 +1322,745 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AEBA7CA-9EE0-40A0-99FB-D58872630BB4}">
+  <dimension ref="B2:D8"/>
+  <sheetFormatPr defaultRowHeight="24" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="24"/>
+    <col min="2" max="2" width="10.28515625" style="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" style="24" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" style="24" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="24"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B3" s="26"/>
+      <c r="C3" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D3" s="27" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B4" s="28"/>
+      <c r="C4" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B5" s="29"/>
+      <c r="C5" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B6" s="30"/>
+      <c r="C6" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B7" s="31"/>
+      <c r="C7" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B8" s="31"/>
+      <c r="C8" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>96</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6551A77-643A-46C2-B44E-DE767D422E77}">
-  <dimension ref="D15:K26"/>
+  <dimension ref="B2:AD19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="14" width="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="23" width="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="2.42578125" customWidth="1"/>
+    <col min="29" max="29" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="6" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="15" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D15" s="3" t="s">
+    <row r="2" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B2" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="H2" s="9">
+        <v>16</v>
+      </c>
+      <c r="I2" s="3">
+        <v>15</v>
+      </c>
+      <c r="J2" s="3">
+        <v>14</v>
+      </c>
+      <c r="K2" s="3">
+        <v>13</v>
+      </c>
+      <c r="L2" s="3">
+        <v>12</v>
+      </c>
+      <c r="M2" s="3">
+        <v>11</v>
+      </c>
+      <c r="N2" s="3">
+        <v>10</v>
+      </c>
+      <c r="O2" s="3">
+        <v>9</v>
+      </c>
+      <c r="P2" s="9">
+        <v>8</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>7</v>
+      </c>
+      <c r="R2" s="3">
+        <v>6</v>
+      </c>
+      <c r="S2" s="3">
+        <v>5</v>
+      </c>
+      <c r="T2" s="3">
+        <v>4</v>
+      </c>
+      <c r="U2" s="3">
+        <v>3</v>
+      </c>
+      <c r="V2" s="5">
+        <v>2</v>
+      </c>
+      <c r="W2" s="9">
+        <v>1</v>
+      </c>
+      <c r="X2" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y2" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z2" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC2" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="AD2" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B3" s="3">
+        <v>0</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0</v>
+      </c>
+      <c r="H3" s="15"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="16"/>
+      <c r="O3" s="16"/>
+      <c r="P3" s="16"/>
+      <c r="Q3" s="16"/>
+      <c r="R3" s="16"/>
+      <c r="S3" s="16"/>
+      <c r="T3" s="16"/>
+      <c r="U3" s="16"/>
+      <c r="V3" s="17"/>
+      <c r="W3" s="14">
+        <v>0</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y3" s="6"/>
+      <c r="Z3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA3" s="6">
+        <v>2</v>
+      </c>
+      <c r="AC3" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="J15" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="K15" s="3" t="s">
+      <c r="AD3" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B4" s="9">
+        <v>1</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="9">
+        <v>1</v>
+      </c>
+      <c r="H4" s="18"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
+      <c r="O4" s="19"/>
+      <c r="P4" s="19"/>
+      <c r="Q4" s="19"/>
+      <c r="R4" s="19"/>
+      <c r="S4" s="19"/>
+      <c r="T4" s="19"/>
+      <c r="U4" s="20"/>
+      <c r="V4" s="12">
+        <v>0</v>
+      </c>
+      <c r="W4" s="13">
+        <v>0</v>
+      </c>
+      <c r="X4" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y4" s="6"/>
+      <c r="Z4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA4" s="6">
+        <v>4</v>
+      </c>
+      <c r="AC4" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD4" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B5" s="9">
+        <v>2</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="9">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0</v>
+      </c>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19"/>
+      <c r="O5" s="19"/>
+      <c r="P5" s="19"/>
+      <c r="Q5" s="19"/>
+      <c r="R5" s="19"/>
+      <c r="S5" s="20"/>
+      <c r="T5" s="12">
+        <v>0</v>
+      </c>
+      <c r="U5" s="13">
+        <v>0</v>
+      </c>
+      <c r="V5" s="13">
+        <v>0</v>
+      </c>
+      <c r="W5" s="13">
+        <v>0</v>
+      </c>
+      <c r="X5" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y5" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA5" s="6">
+        <v>16</v>
+      </c>
+      <c r="AC5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AD5" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B6" s="3">
+        <v>3</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="10">
+        <v>1</v>
+      </c>
+      <c r="F6" s="10">
+        <v>1</v>
+      </c>
+      <c r="H6" s="21"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="23"/>
+      <c r="P6" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2">
+        <v>0</v>
+      </c>
+      <c r="S6" s="2">
+        <v>0</v>
+      </c>
+      <c r="T6" s="2">
+        <v>0</v>
+      </c>
+      <c r="U6" s="2">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2">
+        <v>0</v>
+      </c>
+      <c r="X6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y6" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z6" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA6" s="6">
+        <v>256</v>
+      </c>
+      <c r="AC6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AD6" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B7" s="9">
+        <v>4</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0</v>
+      </c>
+      <c r="D7" s="9">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0</v>
+      </c>
+      <c r="H7" s="8">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2">
+        <v>0</v>
+      </c>
+      <c r="L7" s="2">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2">
+        <v>0</v>
+      </c>
+      <c r="N7" s="2">
+        <v>0</v>
+      </c>
+      <c r="O7" s="2">
+        <v>0</v>
+      </c>
+      <c r="P7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>0</v>
+      </c>
+      <c r="R7" s="2">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2">
+        <v>0</v>
+      </c>
+      <c r="T7" s="2">
+        <v>0</v>
+      </c>
+      <c r="U7" s="2">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2">
+        <v>0</v>
+      </c>
+      <c r="W7" s="2">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y7" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z7" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AA7" s="11">
+        <v>65536</v>
+      </c>
+      <c r="AC7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD7" s="6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B8" s="3">
+        <v>5</v>
+      </c>
+      <c r="C8" s="4">
+        <v>0</v>
+      </c>
+      <c r="D8" s="10">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4">
+        <v>0</v>
+      </c>
+      <c r="F8" s="10">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AD8" s="6">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B9" s="3">
+        <v>6</v>
+      </c>
+      <c r="C9" s="4">
+        <v>0</v>
+      </c>
+      <c r="D9" s="10">
+        <v>1</v>
+      </c>
+      <c r="E9" s="10">
+        <v>1</v>
+      </c>
+      <c r="F9" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AD9" s="6">
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D16" s="3">
-        <v>0</v>
-      </c>
-      <c r="E16" s="5">
-        <v>0</v>
-      </c>
-      <c r="F16" s="5">
-        <v>0</v>
-      </c>
-      <c r="G16" s="5">
-        <v>0</v>
-      </c>
-      <c r="H16" s="5">
-        <v>0</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="K16" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D17" s="3">
-        <v>1</v>
-      </c>
-      <c r="E17" s="5">
-        <v>0</v>
-      </c>
-      <c r="F17" s="5">
-        <v>0</v>
-      </c>
-      <c r="G17" s="5">
-        <v>0</v>
-      </c>
-      <c r="H17" s="6">
-        <v>1</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="K17" s="7">
+    <row r="10" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B10" s="3">
+        <v>7</v>
+      </c>
+      <c r="C10" s="4">
+        <v>0</v>
+      </c>
+      <c r="D10" s="10">
+        <v>1</v>
+      </c>
+      <c r="E10" s="10">
+        <v>1</v>
+      </c>
+      <c r="F10" s="10">
+        <v>1</v>
+      </c>
+      <c r="AC10" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD10" s="6">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="11" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B11" s="9">
+        <v>8</v>
+      </c>
+      <c r="C11" s="9">
+        <v>1</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0</v>
+      </c>
+      <c r="E11" s="4">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD11" s="6">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="12" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B12" s="3">
+        <v>9</v>
+      </c>
+      <c r="C12" s="10">
+        <v>1</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0</v>
+      </c>
+      <c r="E12" s="4">
+        <v>0</v>
+      </c>
+      <c r="F12" s="10">
+        <v>1</v>
+      </c>
+      <c r="AC12" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD12" s="6">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="13" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B13" s="32">
+        <v>10</v>
+      </c>
+      <c r="C13" s="10">
+        <v>1</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0</v>
+      </c>
+      <c r="E13" s="10">
+        <v>1</v>
+      </c>
+      <c r="F13" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD13" s="6">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="14" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B14" s="32">
+        <v>11</v>
+      </c>
+      <c r="C14" s="10">
+        <v>1</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="10">
+        <v>1</v>
+      </c>
+      <c r="F14" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B15" s="32">
+        <v>12</v>
+      </c>
+      <c r="C15" s="10">
+        <v>1</v>
+      </c>
+      <c r="D15" s="10">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B16" s="32">
+        <v>13</v>
+      </c>
+      <c r="C16" s="10">
+        <v>1</v>
+      </c>
+      <c r="D16" s="10">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4">
+        <v>0</v>
+      </c>
+      <c r="F16" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B17" s="32">
+        <v>14</v>
+      </c>
+      <c r="C17" s="10">
+        <v>1</v>
+      </c>
+      <c r="D17" s="10">
+        <v>1</v>
+      </c>
+      <c r="E17" s="10">
+        <v>1</v>
+      </c>
+      <c r="F17" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B18" s="32">
+        <v>25</v>
+      </c>
+      <c r="C18" s="10">
+        <v>1</v>
+      </c>
+      <c r="D18" s="10">
+        <v>1</v>
+      </c>
+      <c r="E18" s="10">
+        <v>1</v>
+      </c>
+      <c r="F18" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B19" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="5">
+        <v>8</v>
+      </c>
+      <c r="D19" s="5">
+        <v>4</v>
+      </c>
+      <c r="E19" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D18" s="3">
-        <v>2</v>
-      </c>
-      <c r="E18" s="5">
-        <v>0</v>
-      </c>
-      <c r="F18" s="5">
-        <v>0</v>
-      </c>
-      <c r="G18" s="6">
-        <v>1</v>
-      </c>
-      <c r="H18" s="5">
-        <v>0</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="K18" s="7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D19" s="3">
-        <v>3</v>
-      </c>
-      <c r="E19" s="5">
-        <v>0</v>
-      </c>
       <c r="F19" s="5">
-        <v>0</v>
-      </c>
-      <c r="G19" s="5">
-        <v>1</v>
-      </c>
-      <c r="H19" s="5">
-        <v>1</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K19" s="7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D20" s="3">
-        <v>4</v>
-      </c>
-      <c r="E20" s="5">
-        <v>0</v>
-      </c>
-      <c r="F20" s="6">
-        <v>1</v>
-      </c>
-      <c r="G20" s="5">
-        <v>0</v>
-      </c>
-      <c r="H20" s="5">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="K20" s="7">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D21" s="3">
-        <v>5</v>
-      </c>
-      <c r="E21" s="5">
-        <v>0</v>
-      </c>
-      <c r="F21" s="5">
-        <v>1</v>
-      </c>
-      <c r="G21" s="5">
-        <v>0</v>
-      </c>
-      <c r="H21" s="5">
-        <v>1</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="K21" s="7">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D22" s="3">
-        <v>6</v>
-      </c>
-      <c r="E22" s="5">
-        <v>0</v>
-      </c>
-      <c r="F22" s="5">
-        <v>1</v>
-      </c>
-      <c r="G22" s="5">
-        <v>1</v>
-      </c>
-      <c r="H22" s="5">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="K22" s="7">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="23" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D23" s="3">
-        <v>7</v>
-      </c>
-      <c r="E23" s="5">
-        <v>0</v>
-      </c>
-      <c r="F23" s="5">
-        <v>1</v>
-      </c>
-      <c r="G23" s="5">
-        <v>1</v>
-      </c>
-      <c r="H23" s="5">
-        <v>1</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="K23" s="7">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="24" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D24" s="3">
-        <v>8</v>
-      </c>
-      <c r="E24" s="6">
-        <v>1</v>
-      </c>
-      <c r="F24" s="5">
-        <v>0</v>
-      </c>
-      <c r="G24" s="5">
-        <v>0</v>
-      </c>
-      <c r="H24" s="5">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="K24" s="7">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="25" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D25" s="3">
-        <v>9</v>
-      </c>
-      <c r="E25" s="5">
-        <v>1</v>
-      </c>
-      <c r="F25" s="5">
-        <v>0</v>
-      </c>
-      <c r="G25" s="5">
-        <v>0</v>
-      </c>
-      <c r="H25" s="5">
-        <v>1</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="K25" s="7">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="26" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D26" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E26" s="6">
-        <v>8</v>
-      </c>
-      <c r="F26" s="6">
-        <v>4</v>
-      </c>
-      <c r="G26" s="6">
-        <v>2</v>
-      </c>
-      <c r="H26" s="6">
-        <v>1</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="K26" s="7">
-        <v>1024</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="E15:H15"/>
+  <mergeCells count="5">
+    <mergeCell ref="H4:U4"/>
+    <mergeCell ref="H3:V3"/>
+    <mergeCell ref="H5:S5"/>
+    <mergeCell ref="H6:O6"/>
+    <mergeCell ref="C2:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Work/Quick Access/Sheets/UI Elements.xlsx
+++ b/Work/Quick Access/Sheets/UI Elements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\Ganesh Notes\Docs\Work\Quick Access\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A43F1EF-8A21-484F-80F1-7BBB4BE95505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{952297A7-2DA0-40A9-A283-16879F9AD9A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{58F146A1-B1DA-4048-895A-7747C642247E}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
     <sheet name="Binary" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="5" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$1</definedName>
@@ -574,7 +575,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -591,9 +592,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -608,33 +606,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -659,7 +630,34 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -670,6 +668,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF000000"/>
       <color rgb="FF3276B1"/>
       <color rgb="FFC79121"/>
       <color rgb="FFA90329"/>
@@ -1326,75 +1325,75 @@
   <dimension ref="B2:D8"/>
   <sheetFormatPr defaultRowHeight="24" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="24"/>
-    <col min="2" max="2" width="10.28515625" style="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" style="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" style="24" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="24"/>
+    <col min="1" max="1" width="9.140625" style="14"/>
+    <col min="2" max="2" width="10.28515625" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" style="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="14"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="D2" s="15" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B3" s="26"/>
-      <c r="C3" s="25" t="s">
+      <c r="B3" s="16"/>
+      <c r="C3" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="17" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B4" s="28"/>
-      <c r="C4" s="25" t="s">
+      <c r="B4" s="18"/>
+      <c r="C4" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="17" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B5" s="29"/>
-      <c r="C5" s="25" t="s">
+      <c r="B5" s="19"/>
+      <c r="C5" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="17" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B6" s="30"/>
-      <c r="C6" s="25" t="s">
+      <c r="B6" s="20"/>
+      <c r="C6" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="17" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B7" s="31"/>
-      <c r="C7" s="25" t="s">
+      <c r="B7" s="21"/>
+      <c r="C7" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="D7" s="17" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B8" s="31"/>
-      <c r="C8" s="25" t="s">
+      <c r="B8" s="21"/>
+      <c r="C8" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="17" t="s">
         <v>96</v>
       </c>
     </row>
@@ -1428,13 +1427,13 @@
       <c r="B2" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="H2" s="9">
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="H2" s="8">
         <v>16</v>
       </c>
       <c r="I2" s="3">
@@ -1458,7 +1457,7 @@
       <c r="O2" s="3">
         <v>9</v>
       </c>
-      <c r="P2" s="9">
+      <c r="P2" s="8">
         <v>8</v>
       </c>
       <c r="Q2" s="3">
@@ -1479,7 +1478,7 @@
       <c r="V2" s="5">
         <v>2</v>
       </c>
-      <c r="W2" s="9">
+      <c r="W2" s="8">
         <v>1</v>
       </c>
       <c r="X2" s="3" t="s">
@@ -1517,22 +1516,22 @@
       <c r="F3" s="4">
         <v>0</v>
       </c>
-      <c r="H3" s="15"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-      <c r="K3" s="16"/>
-      <c r="L3" s="16"/>
-      <c r="M3" s="16"/>
-      <c r="N3" s="16"/>
-      <c r="O3" s="16"/>
-      <c r="P3" s="16"/>
-      <c r="Q3" s="16"/>
-      <c r="R3" s="16"/>
-      <c r="S3" s="16"/>
-      <c r="T3" s="16"/>
-      <c r="U3" s="16"/>
-      <c r="V3" s="17"/>
-      <c r="W3" s="14">
+      <c r="H3" s="25"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
+      <c r="L3" s="26"/>
+      <c r="M3" s="26"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="26"/>
+      <c r="P3" s="26"/>
+      <c r="Q3" s="26"/>
+      <c r="R3" s="26"/>
+      <c r="S3" s="26"/>
+      <c r="T3" s="26"/>
+      <c r="U3" s="26"/>
+      <c r="V3" s="27"/>
+      <c r="W3" s="13">
         <v>0</v>
       </c>
       <c r="X3" s="2" t="s">
@@ -1553,7 +1552,7 @@
       </c>
     </row>
     <row r="4" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="B4" s="9">
+      <c r="B4" s="8">
         <v>1</v>
       </c>
       <c r="C4" s="4">
@@ -1565,27 +1564,27 @@
       <c r="E4" s="4">
         <v>0</v>
       </c>
-      <c r="F4" s="9">
-        <v>1</v>
-      </c>
-      <c r="H4" s="18"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
-      <c r="O4" s="19"/>
-      <c r="P4" s="19"/>
-      <c r="Q4" s="19"/>
-      <c r="R4" s="19"/>
-      <c r="S4" s="19"/>
-      <c r="T4" s="19"/>
-      <c r="U4" s="20"/>
-      <c r="V4" s="12">
-        <v>0</v>
-      </c>
-      <c r="W4" s="13">
+      <c r="F4" s="8">
+        <v>1</v>
+      </c>
+      <c r="H4" s="22"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="23"/>
+      <c r="S4" s="23"/>
+      <c r="T4" s="23"/>
+      <c r="U4" s="24"/>
+      <c r="V4" s="11">
+        <v>0</v>
+      </c>
+      <c r="W4" s="12">
         <v>0</v>
       </c>
       <c r="X4" s="2" t="s">
@@ -1606,7 +1605,7 @@
       </c>
     </row>
     <row r="5" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="B5" s="9">
+      <c r="B5" s="8">
         <v>2</v>
       </c>
       <c r="C5" s="4">
@@ -1615,34 +1614,34 @@
       <c r="D5" s="4">
         <v>0</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="8">
         <v>1</v>
       </c>
       <c r="F5" s="4">
         <v>0</v>
       </c>
-      <c r="H5" s="18"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="19"/>
-      <c r="N5" s="19"/>
-      <c r="O5" s="19"/>
-      <c r="P5" s="19"/>
-      <c r="Q5" s="19"/>
-      <c r="R5" s="19"/>
-      <c r="S5" s="20"/>
-      <c r="T5" s="12">
-        <v>0</v>
-      </c>
-      <c r="U5" s="13">
-        <v>0</v>
-      </c>
-      <c r="V5" s="13">
-        <v>0</v>
-      </c>
-      <c r="W5" s="13">
+      <c r="H5" s="22"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="23"/>
+      <c r="S5" s="24"/>
+      <c r="T5" s="11">
+        <v>0</v>
+      </c>
+      <c r="U5" s="12">
+        <v>0</v>
+      </c>
+      <c r="V5" s="12">
+        <v>0</v>
+      </c>
+      <c r="W5" s="12">
         <v>0</v>
       </c>
       <c r="X5" s="2" t="s">
@@ -1674,21 +1673,21 @@
       <c r="D6" s="4">
         <v>0</v>
       </c>
-      <c r="E6" s="10">
-        <v>1</v>
-      </c>
-      <c r="F6" s="10">
-        <v>1</v>
-      </c>
-      <c r="H6" s="21"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="22"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="22"/>
-      <c r="N6" s="22"/>
-      <c r="O6" s="23"/>
-      <c r="P6" s="8">
+      <c r="E6" s="9">
+        <v>1</v>
+      </c>
+      <c r="F6" s="9">
+        <v>1</v>
+      </c>
+      <c r="H6" s="28"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="29"/>
+      <c r="N6" s="29"/>
+      <c r="O6" s="30"/>
+      <c r="P6" s="7">
         <v>0</v>
       </c>
       <c r="Q6" s="2">
@@ -1732,13 +1731,13 @@
       </c>
     </row>
     <row r="7" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="B7" s="9">
+      <c r="B7" s="8">
         <v>4</v>
       </c>
       <c r="C7" s="4">
         <v>0</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="8">
         <v>1</v>
       </c>
       <c r="E7" s="4">
@@ -1747,7 +1746,7 @@
       <c r="F7" s="4">
         <v>0</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="7">
         <v>0</v>
       </c>
       <c r="I7" s="2">
@@ -1804,7 +1803,7 @@
       <c r="Z7" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="AA7" s="11">
+      <c r="AA7" s="10">
         <v>65536</v>
       </c>
       <c r="AC7" s="3" t="s">
@@ -1821,13 +1820,13 @@
       <c r="C8" s="4">
         <v>0</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="9">
         <v>1</v>
       </c>
       <c r="E8" s="4">
         <v>0</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="9">
         <v>1</v>
       </c>
       <c r="AC8" s="3" t="s">
@@ -1844,10 +1843,10 @@
       <c r="C9" s="4">
         <v>0</v>
       </c>
-      <c r="D9" s="10">
-        <v>1</v>
-      </c>
-      <c r="E9" s="10">
+      <c r="D9" s="9">
+        <v>1</v>
+      </c>
+      <c r="E9" s="9">
         <v>1</v>
       </c>
       <c r="F9" s="4">
@@ -1867,13 +1866,13 @@
       <c r="C10" s="4">
         <v>0</v>
       </c>
-      <c r="D10" s="10">
-        <v>1</v>
-      </c>
-      <c r="E10" s="10">
-        <v>1</v>
-      </c>
-      <c r="F10" s="10">
+      <c r="D10" s="9">
+        <v>1</v>
+      </c>
+      <c r="E10" s="9">
+        <v>1</v>
+      </c>
+      <c r="F10" s="9">
         <v>1</v>
       </c>
       <c r="AC10" s="3" t="s">
@@ -1884,10 +1883,10 @@
       </c>
     </row>
     <row r="11" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="B11" s="9">
+      <c r="B11" s="8">
         <v>8</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="8">
         <v>1</v>
       </c>
       <c r="D11" s="4">
@@ -1910,7 +1909,7 @@
       <c r="B12" s="3">
         <v>9</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="9">
         <v>1</v>
       </c>
       <c r="D12" s="4">
@@ -1919,7 +1918,7 @@
       <c r="E12" s="4">
         <v>0</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="9">
         <v>1</v>
       </c>
       <c r="AC12" s="3" t="s">
@@ -1930,16 +1929,16 @@
       </c>
     </row>
     <row r="13" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="B13" s="32">
+      <c r="B13" s="3">
         <v>10</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="9">
         <v>1</v>
       </c>
       <c r="D13" s="4">
         <v>0</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="9">
         <v>1</v>
       </c>
       <c r="F13" s="4">
@@ -1953,30 +1952,30 @@
       </c>
     </row>
     <row r="14" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="B14" s="32">
+      <c r="B14" s="3">
         <v>11</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="9">
         <v>1</v>
       </c>
       <c r="D14" s="4">
         <v>0</v>
       </c>
-      <c r="E14" s="10">
-        <v>1</v>
-      </c>
-      <c r="F14" s="10">
+      <c r="E14" s="9">
+        <v>1</v>
+      </c>
+      <c r="F14" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="B15" s="32">
+      <c r="B15" s="3">
         <v>12</v>
       </c>
-      <c r="C15" s="10">
-        <v>1</v>
-      </c>
-      <c r="D15" s="10">
+      <c r="C15" s="9">
+        <v>1</v>
+      </c>
+      <c r="D15" s="9">
         <v>1</v>
       </c>
       <c r="E15" s="4">
@@ -1987,33 +1986,33 @@
       </c>
     </row>
     <row r="16" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="B16" s="32">
+      <c r="B16" s="3">
         <v>13</v>
       </c>
-      <c r="C16" s="10">
-        <v>1</v>
-      </c>
-      <c r="D16" s="10">
+      <c r="C16" s="9">
+        <v>1</v>
+      </c>
+      <c r="D16" s="9">
         <v>1</v>
       </c>
       <c r="E16" s="4">
         <v>0</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B17" s="32">
+      <c r="B17" s="3">
         <v>14</v>
       </c>
-      <c r="C17" s="10">
-        <v>1</v>
-      </c>
-      <c r="D17" s="10">
-        <v>1</v>
-      </c>
-      <c r="E17" s="10">
+      <c r="C17" s="9">
+        <v>1</v>
+      </c>
+      <c r="D17" s="9">
+        <v>1</v>
+      </c>
+      <c r="E17" s="9">
         <v>1</v>
       </c>
       <c r="F17" s="4">
@@ -2021,19 +2020,19 @@
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B18" s="32">
+      <c r="B18" s="3">
         <v>25</v>
       </c>
-      <c r="C18" s="10">
-        <v>1</v>
-      </c>
-      <c r="D18" s="10">
-        <v>1</v>
-      </c>
-      <c r="E18" s="10">
-        <v>1</v>
-      </c>
-      <c r="F18" s="10">
+      <c r="C18" s="9">
+        <v>1</v>
+      </c>
+      <c r="D18" s="9">
+        <v>1</v>
+      </c>
+      <c r="E18" s="9">
+        <v>1</v>
+      </c>
+      <c r="F18" s="9">
         <v>1</v>
       </c>
     </row>
@@ -2064,4 +2063,13 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{303C0165-498E-4119-B6F6-E9F40C85B18A}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>